--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -212,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -260,14 +260,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -280,12 +280,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1328,7 +1322,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -1539,7 +1533,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Дефектов: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Приоритет High — 9, Medium — 6, Low — 6. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
+          <t>Дефектов: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Приоритет в карточках не заполнен. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
         </is>
       </c>
     </row>
@@ -1648,11 +1642,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D2" s="19" t="inlineStr"/>
       <c r="E2" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1690,11 +1680,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D3" s="19" t="inlineStr"/>
       <c r="E3" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1732,11 +1718,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D4" s="19" t="inlineStr"/>
       <c r="E4" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1774,11 +1756,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D5" s="19" t="inlineStr"/>
       <c r="E5" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1816,11 +1794,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D6" s="19" t="inlineStr"/>
       <c r="E6" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1858,11 +1832,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D7" s="19" t="inlineStr"/>
       <c r="E7" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1900,11 +1870,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D8" s="19" t="inlineStr"/>
       <c r="E8" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1942,11 +1908,7 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D9" s="19" t="inlineStr"/>
       <c r="E9" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -1984,11 +1946,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D10" s="19" t="inlineStr"/>
       <c r="E10" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2026,11 +1984,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D11" s="19" t="inlineStr"/>
       <c r="E11" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2068,11 +2022,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="D12" s="19" t="inlineStr"/>
       <c r="E12" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2110,11 +2060,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D13" s="19" t="inlineStr"/>
       <c r="E13" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2152,11 +2098,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D14" s="19" t="inlineStr"/>
       <c r="E14" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2194,11 +2136,7 @@
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D15" s="19" t="inlineStr"/>
       <c r="E15" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2236,11 +2174,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D16" s="19" t="inlineStr"/>
       <c r="E16" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2278,11 +2212,7 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D17" s="19" t="inlineStr"/>
       <c r="E17" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2320,11 +2250,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D18" s="19" t="inlineStr"/>
       <c r="E18" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2362,11 +2288,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="D19" s="19" t="inlineStr"/>
       <c r="E19" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2404,11 +2326,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D20" s="19" t="inlineStr"/>
       <c r="E20" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2446,11 +2364,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D21" s="19" t="inlineStr"/>
       <c r="E21" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2488,11 +2402,7 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="D22" s="19" t="inlineStr"/>
       <c r="E22" s="18" t="inlineStr">
         <is>
           <t>New</t>
@@ -2535,12 +2445,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>BUG-001   [Страница] На вкладке браузера нет названия страницы</t>
         </is>
       </c>
-      <c r="B1" s="20" t="n"/>
+      <c r="B1" s="21" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2596,7 +2506,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -2608,11 +2518,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2634,7 +2540,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2690,7 @@
           <t>BUG-002   [Выбор модели] Модель «Cayenne 400» показана как хэтчбек Mercedes-Benz</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
+      <c r="B30" s="21" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2852,11 +2758,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2878,7 +2780,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -3055,7 +2957,7 @@
           <t>BUG-003   [GLC 250D 4MATIC] В списке Engine есть значение OutOfMemoryError</t>
         </is>
       </c>
-      <c r="B84" s="20" t="n"/>
+      <c r="B84" s="21" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -3123,11 +3025,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
@@ -3149,7 +3047,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3223,7 @@
           <t>BUG-004   [GLC 250D 4MATIC] Без смены двигателя в заявку попадает Petrol 2.2</t>
         </is>
       </c>
-      <c r="B138" s="20" t="n"/>
+      <c r="B138" s="21" t="n"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -3393,11 +3291,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B144" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B144" s="5" t="inlineStr"/>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
@@ -3419,7 +3313,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3491,7 @@
           <t>BUG-005   [Подтверждение] При двигателе OutOfMemoryError выводится текст {transmission}</t>
         </is>
       </c>
-      <c r="B192" s="20" t="n"/>
+      <c r="B192" s="21" t="n"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
@@ -3665,11 +3559,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B198" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B198" s="5" t="inlineStr"/>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
@@ -3691,7 +3581,7 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3755,12 @@
     <row r="242" ht="15" customHeight="1"/>
     <row r="243" ht="15" customHeight="1"/>
     <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="19" t="inlineStr">
+      <c r="A246" s="20" t="inlineStr">
         <is>
           <t>BUG-006   [Мастер] Номера шагов идут 1, 2, 4, 5</t>
         </is>
       </c>
-      <c r="B246" s="20" t="n"/>
+      <c r="B246" s="21" t="n"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="4" t="inlineStr">
@@ -3926,7 +3816,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B251" s="21" t="inlineStr">
+      <c r="B251" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3938,11 +3828,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B252" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B252" s="5" t="inlineStr"/>
     </row>
     <row r="253" ht="24" customHeight="1">
       <c r="A253" s="4" t="inlineStr">
@@ -3964,7 +3850,7 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4027,7 @@
           <t>BUG-007   [Мастер] С предыдущего шага нельзя вернуться</t>
         </is>
       </c>
-      <c r="B300" s="20" t="n"/>
+      <c r="B300" s="21" t="n"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
@@ -4209,11 +4095,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B306" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B306" s="5" t="inlineStr"/>
     </row>
     <row r="307" ht="24" customHeight="1">
       <c r="A307" s="4" t="inlineStr">
@@ -4235,7 +4117,7 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4289,12 @@
     <row r="350" ht="15" customHeight="1"/>
     <row r="351" ht="15" customHeight="1"/>
     <row r="354" ht="28" customHeight="1">
-      <c r="A354" s="29" t="inlineStr">
+      <c r="A354" s="27" t="inlineStr">
         <is>
           <t>BUG-008   [Контакты] Пустая заявка уходит в бронирование, в сводке видны шаблоны полей</t>
         </is>
       </c>
-      <c r="B354" s="20" t="n"/>
+      <c r="B354" s="21" t="n"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
@@ -4468,7 +4350,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B359" s="30" t="inlineStr">
+      <c r="B359" s="28" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4480,11 +4362,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B360" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B360" s="5" t="inlineStr"/>
     </row>
     <row r="361" ht="24" customHeight="1">
       <c r="A361" s="4" t="inlineStr">
@@ -4506,7 +4384,7 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4649,7 @@
           <t>BUG-009   [Контакты] Значение из пробелов проходит дальше, и имя в сводке пропадает</t>
         </is>
       </c>
-      <c r="B476" s="20" t="n"/>
+      <c r="B476" s="21" t="n"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
@@ -4839,11 +4717,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B482" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B482" s="5" t="inlineStr"/>
     </row>
     <row r="483" ht="24" customHeight="1">
       <c r="A483" s="4" t="inlineStr">
@@ -4865,7 +4739,7 @@
       </c>
       <c r="B484" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -5041,7 +4915,7 @@
           <t>BUG-010   [Контакты] Поле Age принимает отрицательное число</t>
         </is>
       </c>
-      <c r="B530" s="20" t="n"/>
+      <c r="B530" s="21" t="n"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
@@ -5109,11 +4983,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B536" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B536" s="5" t="inlineStr"/>
     </row>
     <row r="537" ht="24" customHeight="1">
       <c r="A537" s="4" t="inlineStr">
@@ -5135,7 +5005,7 @@
       </c>
       <c r="B538" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5269,7 @@
           <t>BUG-011   [Контакты] Поле телефона принимает буквы</t>
         </is>
       </c>
-      <c r="B652" s="20" t="n"/>
+      <c r="B652" s="21" t="n"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="4" t="inlineStr">
@@ -5467,11 +5337,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B658" s="27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="B658" s="5" t="inlineStr"/>
     </row>
     <row r="659" ht="24" customHeight="1">
       <c r="A659" s="4" t="inlineStr">
@@ -5493,7 +5359,7 @@
       </c>
       <c r="B660" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5536,7 @@
           <t>BUG-012   [Контакты] В поля имени принимаются цифры и знаки</t>
         </is>
       </c>
-      <c r="B706" s="20" t="n"/>
+      <c r="B706" s="21" t="n"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="4" t="inlineStr">
@@ -5738,11 +5604,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B712" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B712" s="5" t="inlineStr"/>
     </row>
     <row r="713" ht="24" customHeight="1">
       <c r="A713" s="4" t="inlineStr">
@@ -5764,7 +5626,7 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5802,7 @@
           <t>BUG-013   [Подтверждение] Длинное имя без пробелов выходит за края страницы</t>
         </is>
       </c>
-      <c r="B760" s="20" t="n"/>
+      <c r="B760" s="21" t="n"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="4" t="inlineStr">
@@ -6008,11 +5870,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B766" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B766" s="5" t="inlineStr"/>
     </row>
     <row r="767" ht="24" customHeight="1">
       <c r="A767" s="4" t="inlineStr">
@@ -6034,7 +5892,7 @@
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6051,12 @@
     <row r="798" ht="15" customHeight="1"/>
     <row r="799" ht="15" customHeight="1"/>
     <row r="802" ht="28" customHeight="1">
-      <c r="A802" s="31" t="inlineStr">
+      <c r="A802" s="29" t="inlineStr">
         <is>
           <t>BUG-014   [Подтверждение] В строке конфигурации перед запятой стоит пробел</t>
         </is>
       </c>
-      <c r="B802" s="20" t="n"/>
+      <c r="B802" s="21" t="n"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="4" t="inlineStr">
@@ -6254,7 +6112,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B807" s="32" t="inlineStr">
+      <c r="B807" s="30" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
@@ -6266,11 +6124,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B808" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B808" s="5" t="inlineStr"/>
     </row>
     <row r="809" ht="24" customHeight="1">
       <c r="A809" s="4" t="inlineStr">
@@ -6292,7 +6146,7 @@
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6316,12 @@
     <row r="852" ht="15" customHeight="1"/>
     <row r="853" ht="15" customHeight="1"/>
     <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="19" t="inlineStr">
+      <c r="A856" s="20" t="inlineStr">
         <is>
           <t>BUG-015   [Тексты] В подписях и фразах мастера есть грамматические ошибки</t>
         </is>
       </c>
-      <c r="B856" s="20" t="n"/>
+      <c r="B856" s="21" t="n"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="4" t="inlineStr">
@@ -6523,7 +6377,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B861" s="21" t="inlineStr">
+      <c r="B861" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -6535,11 +6389,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B862" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B862" s="5" t="inlineStr"/>
     </row>
     <row r="863" ht="24" customHeight="1">
       <c r="A863" s="4" t="inlineStr">
@@ -6561,7 +6411,7 @@
       </c>
       <c r="B864" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6641,7 @@
           <t>BUG-016   [Выбор модели] Быстрые нажатия стрелки накладывают несколько автомобилей друг на друга</t>
         </is>
       </c>
-      <c r="B944" s="20" t="n"/>
+      <c r="B944" s="21" t="n"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="4" t="inlineStr">
@@ -6859,11 +6709,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B950" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B950" s="5" t="inlineStr"/>
     </row>
     <row r="951" ht="24" customHeight="1">
       <c r="A951" s="4" t="inlineStr">
@@ -6885,7 +6731,7 @@
       </c>
       <c r="B952" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -7056,12 +6902,12 @@
     <row r="994" ht="15" customHeight="1"/>
     <row r="995" ht="15" customHeight="1"/>
     <row r="998" ht="28" customHeight="1">
-      <c r="A998" s="19" t="inlineStr">
+      <c r="A998" s="20" t="inlineStr">
         <is>
           <t>BUG-017   [Контакты] Подпись поля не связана с полем и не ставит в него курсор</t>
         </is>
       </c>
-      <c r="B998" s="20" t="n"/>
+      <c r="B998" s="21" t="n"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="4" t="inlineStr">
@@ -7117,7 +6963,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1003" s="21" t="inlineStr">
+      <c r="B1003" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7129,11 +6975,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B1004" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B1004" s="5" t="inlineStr"/>
     </row>
     <row r="1005" ht="24" customHeight="1">
       <c r="A1005" s="4" t="inlineStr">
@@ -7155,7 +6997,7 @@
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7168,12 @@
     <row r="1048" ht="15" customHeight="1"/>
     <row r="1049" ht="15" customHeight="1"/>
     <row r="1052" ht="28" customHeight="1">
-      <c r="A1052" s="19" t="inlineStr">
+      <c r="A1052" s="20" t="inlineStr">
         <is>
           <t>BUG-018   [Выбор модели] Стрелки карусели нельзя нажать с клавиатуры</t>
         </is>
       </c>
-      <c r="B1052" s="20" t="n"/>
+      <c r="B1052" s="21" t="n"/>
     </row>
     <row r="1053" ht="24" customHeight="1">
       <c r="A1053" s="4" t="inlineStr">
@@ -7387,7 +7229,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1057" s="21" t="inlineStr">
+      <c r="B1057" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7399,11 +7241,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B1058" s="28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="B1058" s="5" t="inlineStr"/>
     </row>
     <row r="1059" ht="24" customHeight="1">
       <c r="A1059" s="4" t="inlineStr">
@@ -7425,7 +7263,7 @@
       </c>
       <c r="B1060" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7390,12 @@
       </c>
     </row>
     <row r="1072" ht="28" customHeight="1">
-      <c r="A1072" s="19" t="inlineStr">
+      <c r="A1072" s="20" t="inlineStr">
         <is>
           <t>BUG-019   [Страница] У изображений нет текстовой замены, язык страницы не указан</t>
         </is>
       </c>
-      <c r="B1072" s="20" t="n"/>
+      <c r="B1072" s="21" t="n"/>
     </row>
     <row r="1073" ht="24" customHeight="1">
       <c r="A1073" s="4" t="inlineStr">
@@ -7613,7 +7451,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1077" s="21" t="inlineStr">
+      <c r="B1077" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7625,11 +7463,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B1078" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1078" s="5" t="inlineStr"/>
     </row>
     <row r="1079" ht="24" customHeight="1">
       <c r="A1079" s="4" t="inlineStr">
@@ -7651,7 +7485,7 @@
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7655,12 @@
     <row r="1122" ht="15" customHeight="1"/>
     <row r="1123" ht="15" customHeight="1"/>
     <row r="1126" ht="28" customHeight="1">
-      <c r="A1126" s="19" t="inlineStr">
+      <c r="A1126" s="20" t="inlineStr">
         <is>
           <t>BUG-020   [Благодарность] После Book не показано, что именно забронировано</t>
         </is>
       </c>
-      <c r="B1126" s="20" t="n"/>
+      <c r="B1126" s="21" t="n"/>
     </row>
     <row r="1127" ht="24" customHeight="1">
       <c r="A1127" s="4" t="inlineStr">
@@ -7882,7 +7716,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1131" s="21" t="inlineStr">
+      <c r="B1131" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7894,11 +7728,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B1132" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1132" s="5" t="inlineStr"/>
     </row>
     <row r="1133" ht="24" customHeight="1">
       <c r="A1133" s="4" t="inlineStr">
@@ -7920,7 +7750,7 @@
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -8091,12 +7921,12 @@
     <row r="1176" ht="15" customHeight="1"/>
     <row r="1177" ht="15" customHeight="1"/>
     <row r="1180" ht="28" customHeight="1">
-      <c r="A1180" s="19" t="inlineStr">
+      <c r="A1180" s="20" t="inlineStr">
         <is>
           <t>BUG-021   [Страница] Подключён jQuery 1.11.1, поддержка этой ветки закончена</t>
         </is>
       </c>
-      <c r="B1180" s="20" t="n"/>
+      <c r="B1180" s="21" t="n"/>
     </row>
     <row r="1181" ht="24" customHeight="1">
       <c r="A1181" s="4" t="inlineStr">
@@ -8152,7 +7982,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1185" s="21" t="inlineStr">
+      <c r="B1185" s="22" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -8164,11 +7994,7 @@
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="B1186" s="22" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="B1186" s="5" t="inlineStr"/>
     </row>
     <row r="1187" ht="24" customHeight="1">
       <c r="A1187" s="4" t="inlineStr">
@@ -8190,7 +8016,7 @@
       </c>
       <c r="B1188" s="5" t="inlineStr">
         <is>
-          <t>Дмитрий</t>
+          <t>Павел</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8222,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>IMP-001   В мастере нет даты, времени и дилерского центра</t>
         </is>
@@ -8439,7 +8265,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>IMP-002   Перед Book нет согласия на обработку имени, возраста и телефона</t>
         </is>
@@ -8534,7 +8360,7 @@
           <t>S500 Cabriolet AMG — кабриолет, GLC 250D 4MATIC — кроссовер, CLA SB Standard — универсал. Тип кузова на фото совпадает с подписью.</t>
         </is>
       </c>
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8551,7 +8377,7 @@
           <t>Стрелка вперёд идёт по кругу: S500 Cabriolet AMG, Cayenne 400, GLC 250D 4MATIC, CLA SB Standard. Стрелка назад с первой модели открывает последнюю.</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8568,7 +8394,7 @@
           <t>S500 Cabriolet AMG: Petrol 3.0 и Petrol 3.5, коробка только Automatic. CLA SB Standard: Petrol 2.0 и Diesel 2.0, Automatic и Manual.</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8585,7 +8411,7 @@
           <t>Фамилия Иванов, имя Иван, отчество Иванович отображаются в сводке без искажений.</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8602,7 +8428,7 @@
           <t>Значение &lt;script&gt;alert(1)&lt;/script&gt; в имени выводится текстом. Диалоговое окно не появлялось.</t>
         </is>
       </c>
-      <c r="C6" s="34" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8619,7 +8445,7 @@
           <t>Ivanov / Ivan / Ivanovich / 30 / +375291234567 для S500 Cabriolet AMG доходит до экрана благодарности. Ошибки текстов на этом пути описаны в BUG-014 и BUG-015.</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>
@@ -8636,7 +8462,7 @@
           <t>При загрузке в консоли сообщений не было. На 1440×900 и 1280×800 при обычной длине имени горизонтальная прокрутка не появляется.</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Дефекта нет</t>
         </is>

--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные и подтверждение</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные и подтверждение</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные и подтверждение</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные и подтверждение</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B764" s="5" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B806" s="5" t="inlineStr">
         <is>
-          <t>Подтверждение данных</t>
+          <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
     </row>

--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Без дефекта" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Реестр'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Реестр'!$A$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Реестр'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Без дефекта'!$A$1:$C$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Без дефекта'!$1:$1</definedName>
@@ -1533,7 +1533,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Дефектов: 21. Critical — 1, Major — 11, Minor — 8, Trivial — 1. Приоритет в карточках не заполнен. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
+          <t>Дефектов: 20. Critical — 1, Major — 11, Minor — 7, Trivial — 1. Приоритет в карточках не заполнен. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2386,46 +2386,8 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>[Страница] Подключён jQuery 1.11.1, поддержка этой ветки закончена</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr"/>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>Сторонние библиотеки</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>Всегда (5/5)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -2437,7 +2399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7920,230 +7882,8 @@
     <row r="1175" ht="15" customHeight="1"/>
     <row r="1176" ht="15" customHeight="1"/>
     <row r="1177" ht="15" customHeight="1"/>
-    <row r="1180" ht="28" customHeight="1">
-      <c r="A1180" s="20" t="inlineStr">
-        <is>
-          <t>BUG-021   [Страница] Подключён jQuery 1.11.1, поддержка этой ветки закончена</t>
-        </is>
-      </c>
-      <c r="B1180" s="21" t="n"/>
-    </row>
-    <row r="1181" ht="24" customHeight="1">
-      <c r="A1181" s="4" t="inlineStr">
-        <is>
-          <t>Идентификатор</t>
-        </is>
-      </c>
-      <c r="B1181" s="5" t="inlineStr">
-        <is>
-          <t>BUG-021</t>
-        </is>
-      </c>
-    </row>
-    <row r="1182" ht="24" customHeight="1">
-      <c r="A1182" s="4" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B1182" s="5" t="inlineStr">
-        <is>
-          <t>[Страница] Подключён jQuery 1.11.1, поддержка этой ветки закончена</t>
-        </is>
-      </c>
-    </row>
-    <row r="1183" ht="24" customHeight="1">
-      <c r="A1183" s="4" t="inlineStr">
-        <is>
-          <t>Продукт</t>
-        </is>
-      </c>
-      <c r="B1183" s="5" t="inlineStr">
-        <is>
-          <t>Регистрация на тест-драйв</t>
-        </is>
-      </c>
-    </row>
-    <row r="1184" ht="24" customHeight="1">
-      <c r="A1184" s="4" t="inlineStr">
-        <is>
-          <t>Компонент</t>
-        </is>
-      </c>
-      <c r="B1184" s="5" t="inlineStr">
-        <is>
-          <t>Сторонние библиотеки</t>
-        </is>
-      </c>
-    </row>
-    <row r="1185" ht="24" customHeight="1">
-      <c r="A1185" s="4" t="inlineStr">
-        <is>
-          <t>Серьёзность</t>
-        </is>
-      </c>
-      <c r="B1185" s="22" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="1186" ht="24" customHeight="1">
-      <c r="A1186" s="4" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="B1186" s="5" t="inlineStr"/>
-    </row>
-    <row r="1187" ht="24" customHeight="1">
-      <c r="A1187" s="4" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="B1187" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188" ht="24" customHeight="1">
-      <c r="A1188" s="4" t="inlineStr">
-        <is>
-          <t>Автор</t>
-        </is>
-      </c>
-      <c r="B1188" s="5" t="inlineStr">
-        <is>
-          <t>Павел</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189" ht="24" customHeight="1">
-      <c r="A1189" s="4" t="inlineStr">
-        <is>
-          <t>Дата обнаружения</t>
-        </is>
-      </c>
-      <c r="B1189" s="5" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1190" ht="56" customHeight="1">
-      <c r="A1190" s="4" t="inlineStr">
-        <is>
-          <t>Окружение</t>
-        </is>
-      </c>
-      <c r="B1190" s="5" t="inlineStr">
-        <is>
-          <t>ОС: Linux, десктоп. Браузер: Google Chrome 148.0.7778.96. Окно: 1440×900, масштаб 100%. URL: https://testdrive.andersenlab.com/. Сборка страницы: Last-Modified 23.04.2026 13:11:09 GMT. Проверялась только десктопная версия.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191" ht="24" customHeight="1">
-      <c r="A1191" s="4" t="inlineStr">
-        <is>
-          <t>Предусловия</t>
-        </is>
-      </c>
-      <c r="B1191" s="5" t="inlineStr">
-        <is>
-          <t>Страница загружена.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192" ht="24" customHeight="1">
-      <c r="A1192" s="4" t="inlineStr">
-        <is>
-          <t>Тестовые данные</t>
-        </is>
-      </c>
-      <c r="B1192" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="1193" ht="56" customHeight="1">
-      <c r="A1193" s="4" t="inlineStr">
-        <is>
-          <t>Шаги воспроизведения</t>
-        </is>
-      </c>
-      <c r="B1193" s="5" t="inlineStr">
-        <is>
-          <t>1. Открыть https://testdrive.andersenlab.com/.
-2. В консоли браузера выполнить jQuery.fn.jquery.
-3. В исходном коде страницы найти адрес подключаемого скрипта jQuery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1194" ht="24" customHeight="1">
-      <c r="A1194" s="4" t="inlineStr">
-        <is>
-          <t>Ожидаемый результат</t>
-        </is>
-      </c>
-      <c r="B1194" s="5" t="inlineStr">
-        <is>
-          <t>Страница использует поддерживаемую версию jQuery.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1195" ht="56" customHeight="1">
-      <c r="A1195" s="4" t="inlineStr">
-        <is>
-          <t>Фактический результат</t>
-        </is>
-      </c>
-      <c r="B1195" s="5" t="inlineStr">
-        <is>
-          <t>jQuery.fn.jquery возвращает «1.11.1». Скрипт загружается с https://ajax.googleapis.com/ajax/libs/jquery/1/jquery.min.js. Для ветки 1.x опубликованы CVE-2015-9251, CVE-2019-11358, CVE-2020-11022 и CVE-2020-11023. При загрузке страницы сообщений в консоли не было.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196" ht="24" customHeight="1">
-      <c r="A1196" s="4" t="inlineStr">
-        <is>
-          <t>Воспроизводимость</t>
-        </is>
-      </c>
-      <c r="B1196" s="5" t="inlineStr">
-        <is>
-          <t>Всегда (5/5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197" ht="24" customHeight="1">
-      <c r="A1197" s="4" t="inlineStr">
-        <is>
-          <t>Вложение</t>
-        </is>
-      </c>
-      <c r="B1197" s="5" t="inlineStr">
-        <is>
-          <t>Нет снимка: дефект не виден на изображении, проверка описана в комментарии.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1198" ht="40" customHeight="1">
-      <c r="A1198" s="4" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-      <c r="B1198" s="5" t="inlineStr">
-        <is>
-          <t>Имя со строкой &lt;script&gt;alert(1)&lt;/script&gt; было показано как текст и не выполнилось. Рабочий сценарий эксплуатации на форме не получен. Дефект — в версии библиотеки.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="20">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A530:B530"/>
     <mergeCell ref="A300:B300"/>
@@ -8156,7 +7896,6 @@
     <mergeCell ref="A706:B706"/>
     <mergeCell ref="A1126:B1126"/>
     <mergeCell ref="A354:B354"/>
-    <mergeCell ref="A1180:B1180"/>
     <mergeCell ref="A652:B652"/>
     <mergeCell ref="A246:B246"/>
     <mergeCell ref="A84:B84"/>
@@ -8168,7 +7907,7 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="20" manualBreakCount="20">
+  <rowBreaks count="19" manualBreakCount="19">
     <brk id="29" min="0" max="16383" man="1"/>
     <brk id="83" min="0" max="16383" man="1"/>
     <brk id="137" min="0" max="16383" man="1"/>
@@ -8188,7 +7927,6 @@
     <brk id="1051" min="0" max="16383" man="1"/>
     <brk id="1071" min="0" max="16383" man="1"/>
     <brk id="1125" min="0" max="16383" man="1"/>
-    <brk id="1179" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F9" s="18" t="inlineStr">
         <is>
-          <t>Шаг 3. Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Шаг 3. Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>Шаг 3. Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
-          <t>Шаг 3. Контактные данные и подтверждение</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B534" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="B656" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>Контактные данные</t>
+          <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
     </row>

--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -11,13 +11,10 @@
     <sheet name="Реестр" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Баг-репорты" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Улучшения" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Без дефекта" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Реестр'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Реестр'!$A$1:$H$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Реестр'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Без дефекта'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Без дефекта'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,14 +90,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00196F3D"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -135,21 +126,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5D8DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5B7B1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAD7A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -212,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -240,15 +216,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,9 +263,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,31 +917,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>1145</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7239000" cy="4524375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1270,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1467,98 +1406,35 @@
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Приоритет — порядок исправления</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Уровень</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Когда исправлять</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>До размещения модуля на сайте дилера.</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>В этой же версии. Заявку отправить можно, но клиент видит неверные данные или не может их поправить.</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>После дефектов High и Medium.</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
           <t>Итог</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Дефектов: 20. Critical — 1, Major — 11, Minor — 7, Trivial — 1. Приоритет в карточках не заполнен. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Дефектов: 19. Critical — 1, Major — 11, Minor — 6, Trivial — 1. Улучшений, не включённых в дефекты: 2. Все дефекты воспроизводятся всегда, 5 из 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="15">
+    <mergeCell ref="B3:D3"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B22:D23"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B28:D29"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1571,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1627,14 +1503,14 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>BUG-001</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>[Страница] На вкладке браузера нет названия страницы</t>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>В окне браузера нет названия страницы</t>
         </is>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -1642,35 +1518,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr"/>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr"/>
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
-        <is>
-          <t>Оболочка страницы</t>
-        </is>
-      </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Окно браузера</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>browser-tab-crop.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>BUG-002</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>[Выбор модели] Модель «Cayenne 400» показана как хэтчбек Mercedes-Benz</t>
         </is>
@@ -1680,35 +1556,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr"/>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr"/>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Шаг 1. Выбор модели</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>model-cayenne-400.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>[GLC 250D 4MATIC] В списке Engine есть значение OutOfMemoryError</t>
         </is>
@@ -1718,35 +1594,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr"/>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr"/>
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Шаг 2. Технические характеристики</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>glc-oom-selected.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>BUG-004</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>[GLC 250D 4MATIC] Без смены двигателя в заявку попадает Petrol 2.2</t>
         </is>
@@ -1756,35 +1632,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr"/>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr"/>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Шаг 2. Технические характеристики</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>glc-default-petrol-confirm.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>BUG-005</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>[Подтверждение] При двигателе OutOfMemoryError выводится текст {transmission}</t>
         </is>
@@ -1794,37 +1670,37 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr"/>
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>confirm-transmission-placeholder.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>BUG-006</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>[Мастер] Номера шагов идут 1, 2, 4, 5</t>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Номера шагов идут 1, 2, 4, 5</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1832,37 +1708,37 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>Заголовок мастера</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Шаг 3, 4</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>BUG-007</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>[Мастер] С предыдущего шага нельзя вернуться</t>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>С предыдущего шага нельзя вернуться</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1870,35 +1746,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr"/>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>Навигация мастера</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Навигация приложения</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>browser-back-leaves-wizard.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>BUG-008</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>[Контакты] Пустая заявка уходит в бронирование, в сводке видны шаблоны полей</t>
         </is>
@@ -1908,35 +1784,35 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr"/>
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>confirm-empty-placeholders.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>BUG-009</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>[Контакты] Значение из пробелов проходит дальше, и имя в сводке пропадает</t>
         </is>
@@ -1946,35 +1822,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr"/>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>confirm-whitespace.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>BUG-010</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>[Контакты] Поле Age принимает отрицательное число</t>
         </is>
@@ -1984,35 +1860,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr"/>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>BUG-011</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>[Контакты] Поле телефона принимает буквы</t>
         </is>
@@ -2022,35 +1898,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr"/>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>BUG-012</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>[Контакты] В поля имени принимаются цифры и знаки</t>
         </is>
@@ -2060,35 +1936,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>confirm-symbols.png</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>BUG-013</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>[Подтверждение] Длинное имя без пробелов выходит за края страницы</t>
         </is>
@@ -2098,35 +1974,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr"/>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>confirm-long-name-overflow.png</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>BUG-014</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>[Подтверждение] В строке конфигурации перед запятой стоит пробел</t>
         </is>
@@ -2136,37 +2012,37 @@
           <t>Trivial</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr"/>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Шаг 4. Подтверждение данных</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>confirm-valid-punctuation.png</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>BUG-015</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>[Тексты] В подписях и фразах мастера есть грамматические ошибки</t>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>[Тексты] В подписях и фразах есть грамматические ошибки</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -2174,35 +2050,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr"/>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>Тексты интерфейса</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>step2-transmissions-label.png</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>BUG-016</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>[Выбор модели] Быстрые нажатия стрелки накладывают несколько автомобилей друг на друга</t>
         </is>
@@ -2212,35 +2088,35 @@
           <t>Major</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr"/>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Шаг 1. Выбор модели</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>carousel-rapid-clicks.png</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>BUG-017</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>[Контакты] Подпись поля не связана с полем и не ставит в него курсор</t>
         </is>
@@ -2250,35 +2126,35 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr"/>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Шаг 3. Контактные данные</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>BUG-018</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>[Выбор модели] Стрелки карусели нельзя нажать с клавиатуры</t>
         </is>
@@ -2288,37 +2164,37 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr"/>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Шаг 1. Выбор модели</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>BUG-019</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>[Страница] У изображений нет текстовой замены, язык страницы не указан</t>
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>BUG-020</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>[Благодарность] После Book не показано, что именно забронировано</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -2326,68 +2202,30 @@
           <t>Minor</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr"/>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr"/>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>Оболочка страницы</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Шаг 5. Экран благодарности</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>Всегда (5/5)</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>model-s500.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>[Благодарность] После Book не показано, что именно забронировано</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr"/>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>Экран благодарности</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>Всегда (5/5)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>thank-you.png</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -2399,7 +2237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B1145"/>
+  <dimension ref="A1:B1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2407,12 +2245,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>BUG-001   [Страница] На вкладке браузера нет названия страницы</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="n"/>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>BUG-001   В окне браузера нет названия страницы</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2434,7 +2272,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>[Страница] На вкладке браузера нет названия страницы</t>
+          <t>В окне браузера нет названия страницы</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2296,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Оболочка страницы</t>
+          <t>Окно браузера</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2306,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -2628,12 +2466,12 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>browser-tab-crop.png</t>
         </is>
@@ -2647,12 +2485,12 @@
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>BUG-002   [Выбор модели] Модель «Cayenne 400» показана как хэтчбек Mercedes-Benz</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n"/>
+      <c r="B30" s="18" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -2708,7 +2546,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -2870,12 +2708,12 @@
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B49" s="24" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>model-cayenne-400.png</t>
         </is>
@@ -2914,12 +2752,12 @@
     <row r="80" ht="15" customHeight="1"/>
     <row r="81" ht="15" customHeight="1"/>
     <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="25" t="inlineStr">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>BUG-003   [GLC 250D 4MATIC] В списке Engine есть значение OutOfMemoryError</t>
         </is>
       </c>
-      <c r="B84" s="21" t="n"/>
+      <c r="B84" s="18" t="n"/>
     </row>
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -2975,7 +2813,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B89" s="26" t="inlineStr">
+      <c r="B89" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3136,12 +2974,12 @@
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="23" t="inlineStr">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B103" s="24" t="inlineStr">
+      <c r="B103" s="21" t="inlineStr">
         <is>
           <t>glc-oom-selected.png</t>
         </is>
@@ -3180,12 +3018,12 @@
     <row r="134" ht="15" customHeight="1"/>
     <row r="135" ht="15" customHeight="1"/>
     <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="25" t="inlineStr">
+      <c r="A138" s="22" t="inlineStr">
         <is>
           <t>BUG-004   [GLC 250D 4MATIC] Без смены двигателя в заявку попадает Petrol 2.2</t>
         </is>
       </c>
-      <c r="B138" s="21" t="n"/>
+      <c r="B138" s="18" t="n"/>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
@@ -3241,7 +3079,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B143" s="26" t="inlineStr">
+      <c r="B143" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3404,12 +3242,12 @@
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="23" t="inlineStr">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B157" s="24" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>glc-default-petrol-confirm.png</t>
         </is>
@@ -3448,12 +3286,12 @@
     <row r="188" ht="15" customHeight="1"/>
     <row r="189" ht="15" customHeight="1"/>
     <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="25" t="inlineStr">
+      <c r="A192" s="22" t="inlineStr">
         <is>
           <t>BUG-005   [Подтверждение] При двигателе OutOfMemoryError выводится текст {transmission}</t>
         </is>
       </c>
-      <c r="B192" s="21" t="n"/>
+      <c r="B192" s="18" t="n"/>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
@@ -3509,7 +3347,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B197" s="26" t="inlineStr">
+      <c r="B197" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3673,12 +3511,12 @@
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="23" t="inlineStr">
+      <c r="A211" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B211" s="24" t="inlineStr">
+      <c r="B211" s="21" t="inlineStr">
         <is>
           <t>confirm-transmission-placeholder.png</t>
         </is>
@@ -3717,12 +3555,12 @@
     <row r="242" ht="15" customHeight="1"/>
     <row r="243" ht="15" customHeight="1"/>
     <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="20" t="inlineStr">
-        <is>
-          <t>BUG-006   [Мастер] Номера шагов идут 1, 2, 4, 5</t>
-        </is>
-      </c>
-      <c r="B246" s="21" t="n"/>
+      <c r="A246" s="17" t="inlineStr">
+        <is>
+          <t>BUG-006   Номера шагов идут 1, 2, 4, 5</t>
+        </is>
+      </c>
+      <c r="B246" s="18" t="n"/>
     </row>
     <row r="247" ht="24" customHeight="1">
       <c r="A247" s="4" t="inlineStr">
@@ -3744,7 +3582,7 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>[Мастер] Номера шагов идут 1, 2, 4, 5</t>
+          <t>Номера шагов идут 1, 2, 4, 5</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3606,7 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Заголовок мастера</t>
+          <t>Шаг 3, 4</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3616,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B251" s="22" t="inlineStr">
+      <c r="B251" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3940,12 +3778,12 @@
       </c>
     </row>
     <row r="265" ht="18" customHeight="1">
-      <c r="A265" s="23" t="inlineStr">
+      <c r="A265" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B265" s="24" t="inlineStr">
+      <c r="B265" s="21" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
@@ -3984,12 +3822,12 @@
     <row r="296" ht="15" customHeight="1"/>
     <row r="297" ht="15" customHeight="1"/>
     <row r="300" ht="28" customHeight="1">
-      <c r="A300" s="25" t="inlineStr">
-        <is>
-          <t>BUG-007   [Мастер] С предыдущего шага нельзя вернуться</t>
-        </is>
-      </c>
-      <c r="B300" s="21" t="n"/>
+      <c r="A300" s="22" t="inlineStr">
+        <is>
+          <t>BUG-007   С предыдущего шага нельзя вернуться</t>
+        </is>
+      </c>
+      <c r="B300" s="18" t="n"/>
     </row>
     <row r="301" ht="24" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
@@ -4011,7 +3849,7 @@
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>[Мастер] С предыдущего шага нельзя вернуться</t>
+          <t>С предыдущего шага нельзя вернуться</t>
         </is>
       </c>
     </row>
@@ -4035,7 +3873,7 @@
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>Навигация мастера</t>
+          <t>Навигация приложения</t>
         </is>
       </c>
     </row>
@@ -4045,7 +3883,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B305" s="26" t="inlineStr">
+      <c r="B305" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -4154,7 +3992,7 @@
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>На втором и следующих шагах есть переход назад, и уже сделанный выбор сохраняется. Кнопка «Назад» браузера открывает предыдущий шаг мастера.</t>
+          <t>На втором и следующих шагах есть переход назад, и уже сделанный выбор сохраняется. Кнопка «Назад» браузера открывает предыдущий шаг приложения.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4004,7 @@
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>На экранах мастера есть только Continue. На подтверждении есть только Book. Кнопки возврата нет. Кнопка «Назад» браузера уходит с testdrive.andersenlab.com на предыдущий сайт. В этой проверке открылся https://example.com/. Модель, двигатель и контакты исправить нельзя.</t>
+          <t>На экранах приложения есть только Continue. На подтверждении есть только Book. Кнопки возврата нет. Кнопка «Назад» браузера уходит с testdrive.andersenlab.com на предыдущий сайт. В этой проверке открылся https://example.com/. Модель, двигатель и контакты исправить нельзя.</t>
         </is>
       </c>
     </row>
@@ -4207,12 +4045,12 @@
       </c>
     </row>
     <row r="319" ht="18" customHeight="1">
-      <c r="A319" s="23" t="inlineStr">
+      <c r="A319" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B319" s="24" t="inlineStr">
+      <c r="B319" s="21" t="inlineStr">
         <is>
           <t>browser-back-leaves-wizard.png</t>
         </is>
@@ -4251,12 +4089,12 @@
     <row r="350" ht="15" customHeight="1"/>
     <row r="351" ht="15" customHeight="1"/>
     <row r="354" ht="28" customHeight="1">
-      <c r="A354" s="27" t="inlineStr">
+      <c r="A354" s="24" t="inlineStr">
         <is>
           <t>BUG-008   [Контакты] Пустая заявка уходит в бронирование, в сводке видны шаблоны полей</t>
         </is>
       </c>
-      <c r="B354" s="21" t="n"/>
+      <c r="B354" s="18" t="n"/>
     </row>
     <row r="355" ht="24" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
@@ -4312,7 +4150,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B359" s="28" t="inlineStr">
+      <c r="B359" s="25" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4433,7 +4271,7 @@
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>Continue открывает подтверждение. Текст на экране: «Your name is {lastName} {firstName} {middleName} and you are {age} years old.» и «Phone number we can reach you at {phone}.» Сообщения об ошибке нет. Book завершает мастер. Далее показаны «Thank you for booking the test drive!» и «Our managers will contact you within next 12 hours.»</t>
+          <t>Continue открывает подтверждение. Текст на экране: «Your name is {lastName} {firstName} {middleName} and you are {age} years old.» и «Phone number we can reach you at {phone}.» Сообщения об ошибке нет. Book завершает приложение. Далее показаны «Thank you for booking the test drive!» и «Our managers will contact you within next 12 hours.»</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4312,12 @@
       </c>
     </row>
     <row r="373" ht="18" customHeight="1">
-      <c r="A373" s="23" t="inlineStr">
+      <c r="A373" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B373" s="24" t="inlineStr">
+      <c r="B373" s="21" t="inlineStr">
         <is>
           <t>confirm-empty-placeholders.png</t>
         </is>
@@ -4518,12 +4356,12 @@
     <row r="404" ht="15" customHeight="1"/>
     <row r="405" ht="15" customHeight="1"/>
     <row r="407" ht="18" customHeight="1">
-      <c r="A407" s="23" t="inlineStr">
+      <c r="A407" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B407" s="24" t="inlineStr">
+      <c r="B407" s="21" t="inlineStr">
         <is>
           <t>empty-booked-thanks.png</t>
         </is>
@@ -4562,12 +4400,12 @@
     <row r="438" ht="15" customHeight="1"/>
     <row r="439" ht="15" customHeight="1"/>
     <row r="441" ht="18" customHeight="1">
-      <c r="A441" s="23" t="inlineStr">
+      <c r="A441" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B441" s="24" t="inlineStr">
+      <c r="B441" s="21" t="inlineStr">
         <is>
           <t>confirm-missing-middle-name.png</t>
         </is>
@@ -4606,12 +4444,12 @@
     <row r="472" ht="15" customHeight="1"/>
     <row r="473" ht="15" customHeight="1"/>
     <row r="476" ht="28" customHeight="1">
-      <c r="A476" s="25" t="inlineStr">
+      <c r="A476" s="22" t="inlineStr">
         <is>
           <t>BUG-009   [Контакты] Значение из пробелов проходит дальше, и имя в сводке пропадает</t>
         </is>
       </c>
-      <c r="B476" s="21" t="n"/>
+      <c r="B476" s="18" t="n"/>
     </row>
     <row r="477" ht="24" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
@@ -4667,7 +4505,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B481" s="26" t="inlineStr">
+      <c r="B481" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -4828,12 +4666,12 @@
       </c>
     </row>
     <row r="495" ht="18" customHeight="1">
-      <c r="A495" s="23" t="inlineStr">
+      <c r="A495" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B495" s="24" t="inlineStr">
+      <c r="B495" s="21" t="inlineStr">
         <is>
           <t>confirm-whitespace.png</t>
         </is>
@@ -4872,12 +4710,12 @@
     <row r="526" ht="15" customHeight="1"/>
     <row r="527" ht="15" customHeight="1"/>
     <row r="530" ht="28" customHeight="1">
-      <c r="A530" s="25" t="inlineStr">
+      <c r="A530" s="22" t="inlineStr">
         <is>
           <t>BUG-010   [Контакты] Поле Age принимает отрицательное число</t>
         </is>
       </c>
-      <c r="B530" s="21" t="n"/>
+      <c r="B530" s="18" t="n"/>
     </row>
     <row r="531" ht="24" customHeight="1">
       <c r="A531" s="4" t="inlineStr">
@@ -4933,7 +4771,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B535" s="26" t="inlineStr">
+      <c r="B535" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5094,12 +4932,12 @@
       </c>
     </row>
     <row r="549" ht="18" customHeight="1">
-      <c r="A549" s="23" t="inlineStr">
+      <c r="A549" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B549" s="24" t="inlineStr">
+      <c r="B549" s="21" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
@@ -5138,12 +4976,12 @@
     <row r="580" ht="15" customHeight="1"/>
     <row r="581" ht="15" customHeight="1"/>
     <row r="583" ht="18" customHeight="1">
-      <c r="A583" s="23" t="inlineStr">
+      <c r="A583" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B583" s="24" t="inlineStr">
+      <c r="B583" s="21" t="inlineStr">
         <is>
           <t>confirm-age-text.png</t>
         </is>
@@ -5182,12 +5020,12 @@
     <row r="614" ht="15" customHeight="1"/>
     <row r="615" ht="15" customHeight="1"/>
     <row r="617" ht="18" customHeight="1">
-      <c r="A617" s="23" t="inlineStr">
+      <c r="A617" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B617" s="24" t="inlineStr">
+      <c r="B617" s="21" t="inlineStr">
         <is>
           <t>confirm-age-15.png</t>
         </is>
@@ -5226,12 +5064,12 @@
     <row r="648" ht="15" customHeight="1"/>
     <row r="649" ht="15" customHeight="1"/>
     <row r="652" ht="28" customHeight="1">
-      <c r="A652" s="25" t="inlineStr">
+      <c r="A652" s="22" t="inlineStr">
         <is>
           <t>BUG-011   [Контакты] Поле телефона принимает буквы</t>
         </is>
       </c>
-      <c r="B652" s="21" t="n"/>
+      <c r="B652" s="18" t="n"/>
     </row>
     <row r="653" ht="24" customHeight="1">
       <c r="A653" s="4" t="inlineStr">
@@ -5287,7 +5125,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B657" s="26" t="inlineStr">
+      <c r="B657" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5449,12 +5287,12 @@
       </c>
     </row>
     <row r="671" ht="18" customHeight="1">
-      <c r="A671" s="23" t="inlineStr">
+      <c r="A671" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B671" s="24" t="inlineStr">
+      <c r="B671" s="21" t="inlineStr">
         <is>
           <t>confirm-invalid-age-phone.png</t>
         </is>
@@ -5493,12 +5331,12 @@
     <row r="702" ht="15" customHeight="1"/>
     <row r="703" ht="15" customHeight="1"/>
     <row r="706" ht="28" customHeight="1">
-      <c r="A706" s="25" t="inlineStr">
+      <c r="A706" s="22" t="inlineStr">
         <is>
           <t>BUG-012   [Контакты] В поля имени принимаются цифры и знаки</t>
         </is>
       </c>
-      <c r="B706" s="21" t="n"/>
+      <c r="B706" s="18" t="n"/>
     </row>
     <row r="707" ht="24" customHeight="1">
       <c r="A707" s="4" t="inlineStr">
@@ -5554,7 +5392,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B711" s="26" t="inlineStr">
+      <c r="B711" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5715,12 +5553,12 @@
       </c>
     </row>
     <row r="725" ht="18" customHeight="1">
-      <c r="A725" s="23" t="inlineStr">
+      <c r="A725" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B725" s="24" t="inlineStr">
+      <c r="B725" s="21" t="inlineStr">
         <is>
           <t>confirm-symbols.png</t>
         </is>
@@ -5759,12 +5597,12 @@
     <row r="756" ht="15" customHeight="1"/>
     <row r="757" ht="15" customHeight="1"/>
     <row r="760" ht="28" customHeight="1">
-      <c r="A760" s="25" t="inlineStr">
+      <c r="A760" s="22" t="inlineStr">
         <is>
           <t>BUG-013   [Подтверждение] Длинное имя без пробелов выходит за края страницы</t>
         </is>
       </c>
-      <c r="B760" s="21" t="n"/>
+      <c r="B760" s="18" t="n"/>
     </row>
     <row r="761" ht="24" customHeight="1">
       <c r="A761" s="4" t="inlineStr">
@@ -5820,7 +5658,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B765" s="26" t="inlineStr">
+      <c r="B765" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -5981,12 +5819,12 @@
       </c>
     </row>
     <row r="779" ht="18" customHeight="1">
-      <c r="A779" s="23" t="inlineStr">
+      <c r="A779" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B779" s="24" t="inlineStr">
+      <c r="B779" s="21" t="inlineStr">
         <is>
           <t>confirm-long-name-overflow.png</t>
         </is>
@@ -6013,12 +5851,12 @@
     <row r="798" ht="15" customHeight="1"/>
     <row r="799" ht="15" customHeight="1"/>
     <row r="802" ht="28" customHeight="1">
-      <c r="A802" s="29" t="inlineStr">
+      <c r="A802" s="26" t="inlineStr">
         <is>
           <t>BUG-014   [Подтверждение] В строке конфигурации перед запятой стоит пробел</t>
         </is>
       </c>
-      <c r="B802" s="21" t="n"/>
+      <c r="B802" s="18" t="n"/>
     </row>
     <row r="803" ht="24" customHeight="1">
       <c r="A803" s="4" t="inlineStr">
@@ -6074,7 +5912,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B807" s="30" t="inlineStr">
+      <c r="B807" s="27" t="inlineStr">
         <is>
           <t>Trivial</t>
         </is>
@@ -6234,12 +6072,12 @@
       </c>
     </row>
     <row r="821" ht="18" customHeight="1">
-      <c r="A821" s="23" t="inlineStr">
+      <c r="A821" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B821" s="24" t="inlineStr">
+      <c r="B821" s="21" t="inlineStr">
         <is>
           <t>confirm-valid-punctuation.png</t>
         </is>
@@ -6278,12 +6116,12 @@
     <row r="852" ht="15" customHeight="1"/>
     <row r="853" ht="15" customHeight="1"/>
     <row r="856" ht="28" customHeight="1">
-      <c r="A856" s="20" t="inlineStr">
-        <is>
-          <t>BUG-015   [Тексты] В подписях и фразах мастера есть грамматические ошибки</t>
-        </is>
-      </c>
-      <c r="B856" s="21" t="n"/>
+      <c r="A856" s="17" t="inlineStr">
+        <is>
+          <t>BUG-015   [Тексты] В подписях и фразах есть грамматические ошибки</t>
+        </is>
+      </c>
+      <c r="B856" s="18" t="n"/>
     </row>
     <row r="857" ht="24" customHeight="1">
       <c r="A857" s="4" t="inlineStr">
@@ -6305,7 +6143,7 @@
       </c>
       <c r="B858" s="5" t="inlineStr">
         <is>
-          <t>[Тексты] В подписях и фразах мастера есть грамматические ошибки</t>
+          <t>[Тексты] В подписях и фразах есть грамматические ошибки</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6177,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B861" s="22" t="inlineStr">
+      <c r="B861" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -6409,7 +6247,7 @@
       </c>
       <c r="B867" s="5" t="inlineStr">
         <is>
-          <t>Можно пройти мастер до экрана благодарности.</t>
+          <t>Можно пройти приложение до экрана благодарности.</t>
         </is>
       </c>
     </row>
@@ -6510,12 +6348,12 @@
       </c>
     </row>
     <row r="875" ht="18" customHeight="1">
-      <c r="A875" s="23" t="inlineStr">
+      <c r="A875" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B875" s="24" t="inlineStr">
+      <c r="B875" s="21" t="inlineStr">
         <is>
           <t>step2-transmissions-label.png</t>
         </is>
@@ -6554,12 +6392,12 @@
     <row r="906" ht="15" customHeight="1"/>
     <row r="907" ht="15" customHeight="1"/>
     <row r="909" ht="18" customHeight="1">
-      <c r="A909" s="23" t="inlineStr">
+      <c r="A909" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B909" s="24" t="inlineStr">
+      <c r="B909" s="21" t="inlineStr">
         <is>
           <t>thank-you.png</t>
         </is>
@@ -6598,12 +6436,12 @@
     <row r="940" ht="15" customHeight="1"/>
     <row r="941" ht="15" customHeight="1"/>
     <row r="944" ht="28" customHeight="1">
-      <c r="A944" s="25" t="inlineStr">
+      <c r="A944" s="22" t="inlineStr">
         <is>
           <t>BUG-016   [Выбор модели] Быстрые нажатия стрелки накладывают несколько автомобилей друг на друга</t>
         </is>
       </c>
-      <c r="B944" s="21" t="n"/>
+      <c r="B944" s="18" t="n"/>
     </row>
     <row r="945" ht="24" customHeight="1">
       <c r="A945" s="4" t="inlineStr">
@@ -6659,7 +6497,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B949" s="26" t="inlineStr">
+      <c r="B949" s="23" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -6820,12 +6658,12 @@
       </c>
     </row>
     <row r="963" ht="18" customHeight="1">
-      <c r="A963" s="23" t="inlineStr">
+      <c r="A963" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B963" s="24" t="inlineStr">
+      <c r="B963" s="21" t="inlineStr">
         <is>
           <t>carousel-rapid-clicks.png</t>
         </is>
@@ -6864,12 +6702,12 @@
     <row r="994" ht="15" customHeight="1"/>
     <row r="995" ht="15" customHeight="1"/>
     <row r="998" ht="28" customHeight="1">
-      <c r="A998" s="20" t="inlineStr">
+      <c r="A998" s="17" t="inlineStr">
         <is>
           <t>BUG-017   [Контакты] Подпись поля не связана с полем и не ставит в него курсор</t>
         </is>
       </c>
-      <c r="B998" s="21" t="n"/>
+      <c r="B998" s="18" t="n"/>
     </row>
     <row r="999" ht="24" customHeight="1">
       <c r="A999" s="4" t="inlineStr">
@@ -6925,7 +6763,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1003" s="22" t="inlineStr">
+      <c r="B1003" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7086,12 +6924,12 @@
       </c>
     </row>
     <row r="1017" ht="18" customHeight="1">
-      <c r="A1017" s="23" t="inlineStr">
+      <c r="A1017" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B1017" s="24" t="inlineStr">
+      <c r="B1017" s="21" t="inlineStr">
         <is>
           <t>contact-step-numbered-4.png</t>
         </is>
@@ -7130,12 +6968,12 @@
     <row r="1048" ht="15" customHeight="1"/>
     <row r="1049" ht="15" customHeight="1"/>
     <row r="1052" ht="28" customHeight="1">
-      <c r="A1052" s="20" t="inlineStr">
+      <c r="A1052" s="17" t="inlineStr">
         <is>
           <t>BUG-018   [Выбор модели] Стрелки карусели нельзя нажать с клавиатуры</t>
         </is>
       </c>
-      <c r="B1052" s="21" t="n"/>
+      <c r="B1052" s="18" t="n"/>
     </row>
     <row r="1053" ht="24" customHeight="1">
       <c r="A1053" s="4" t="inlineStr">
@@ -7191,7 +7029,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1057" s="22" t="inlineStr">
+      <c r="B1057" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7352,12 +7190,12 @@
       </c>
     </row>
     <row r="1072" ht="28" customHeight="1">
-      <c r="A1072" s="20" t="inlineStr">
-        <is>
-          <t>BUG-019   [Страница] У изображений нет текстовой замены, язык страницы не указан</t>
-        </is>
-      </c>
-      <c r="B1072" s="21" t="n"/>
+      <c r="A1072" s="17" t="inlineStr">
+        <is>
+          <t>BUG-020   [Благодарность] После Book не показано, что именно забронировано</t>
+        </is>
+      </c>
+      <c r="B1072" s="18" t="n"/>
     </row>
     <row r="1073" ht="24" customHeight="1">
       <c r="A1073" s="4" t="inlineStr">
@@ -7367,7 +7205,7 @@
       </c>
       <c r="B1073" s="5" t="inlineStr">
         <is>
-          <t>BUG-019</t>
+          <t>BUG-020</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7217,7 @@
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>[Страница] У изображений нет текстовой замены, язык страницы не указан</t>
+          <t>[Благодарность] После Book не показано, что именно забронировано</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7241,7 @@
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>Оболочка страницы</t>
+          <t>Шаг 5. Экран благодарности</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7251,7 @@
           <t>Серьёзность</t>
         </is>
       </c>
-      <c r="B1077" s="22" t="inlineStr">
+      <c r="B1077" s="19" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -7483,7 +7321,7 @@
       </c>
       <c r="B1083" s="5" t="inlineStr">
         <is>
-          <t>Страница регистрации открыта.</t>
+          <t>Открыто подтверждение с заполненными моделью и телефоном.</t>
         </is>
       </c>
     </row>
@@ -7495,11 +7333,11 @@
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="1085" ht="40" customHeight="1">
+          <t>Любая модель и телефон, которые уже видны на подтверждении.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085" ht="56" customHeight="1">
       <c r="A1085" s="4" t="inlineStr">
         <is>
           <t>Шаги воспроизведения</t>
@@ -7507,12 +7345,13 @@
       </c>
       <c r="B1085" s="5" t="inlineStr">
         <is>
-          <t>1. Проверить текстовую замену у логотипа и у четырёх фотографий автомобилей.
-2. Проверить язык, заданный у корневого элемента страницы.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1086" ht="40" customHeight="1">
+          <t>1. Нажать Book.
+2. Прочитать экран благодарности.
+3. Найти на нём модель, конфигурацию, телефон и действие для новой заявки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086" ht="56" customHeight="1">
       <c r="A1086" s="4" t="inlineStr">
         <is>
           <t>Ожидаемый результат</t>
@@ -7520,11 +7359,11 @@
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>У логотипа и у каждой фотографии есть текстовая замена с названием. У страницы указан язык: английский.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1087" ht="40" customHeight="1">
+          <t>На экране повторяются модель, конфигурация и телефон с предыдущего шага. Есть понятное действие, чтобы начать другую заявку. Номер сохранённой заявки не ожидается: сохранение пользователя в этот модуль не входит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087" ht="56" customHeight="1">
       <c r="A1087" s="4" t="inlineStr">
         <is>
           <t>Фактический результат</t>
@@ -7532,7 +7371,7 @@
       </c>
       <c r="B1087" s="5" t="inlineStr">
         <is>
-          <t>Атрибут alt отсутствует у логотипа и у всех четырёх фотографий. У корневого элемента html атрибут lang отсутствует.</t>
+          <t>На экране только «Thank you for booking the test drive!» и «Our managers will contact you within next 12 hours.» Модель и телефон не повторяются. Кнопки для новой заявки нет. Чтобы начать сначала, страницу нужно обновить вручную.</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7395,7 @@
       </c>
       <c r="B1089" s="5" t="inlineStr">
         <is>
-          <t>model-s500.png</t>
+          <t>thank-you.png</t>
         </is>
       </c>
     </row>
@@ -7568,19 +7407,19 @@
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>Пустой заголовок вкладки описан отдельно в BUG-001.</t>
+          <t>Пропущенный артикль в фразе про 12 часов описан в BUG-015.</t>
         </is>
       </c>
     </row>
     <row r="1091" ht="18" customHeight="1">
-      <c r="A1091" s="23" t="inlineStr">
+      <c r="A1091" s="20" t="inlineStr">
         <is>
           <t>Снимок</t>
         </is>
       </c>
-      <c r="B1091" s="24" t="inlineStr">
-        <is>
-          <t>model-s500.png</t>
+      <c r="B1091" s="21" t="inlineStr">
+        <is>
+          <t>thank-you.png</t>
         </is>
       </c>
     </row>
@@ -7616,274 +7455,8 @@
     <row r="1121" ht="15" customHeight="1"/>
     <row r="1122" ht="15" customHeight="1"/>
     <row r="1123" ht="15" customHeight="1"/>
-    <row r="1126" ht="28" customHeight="1">
-      <c r="A1126" s="20" t="inlineStr">
-        <is>
-          <t>BUG-020   [Благодарность] После Book не показано, что именно забронировано</t>
-        </is>
-      </c>
-      <c r="B1126" s="21" t="n"/>
-    </row>
-    <row r="1127" ht="24" customHeight="1">
-      <c r="A1127" s="4" t="inlineStr">
-        <is>
-          <t>Идентификатор</t>
-        </is>
-      </c>
-      <c r="B1127" s="5" t="inlineStr">
-        <is>
-          <t>BUG-020</t>
-        </is>
-      </c>
-    </row>
-    <row r="1128" ht="24" customHeight="1">
-      <c r="A1128" s="4" t="inlineStr">
-        <is>
-          <t>Заголовок</t>
-        </is>
-      </c>
-      <c r="B1128" s="5" t="inlineStr">
-        <is>
-          <t>[Благодарность] После Book не показано, что именно забронировано</t>
-        </is>
-      </c>
-    </row>
-    <row r="1129" ht="24" customHeight="1">
-      <c r="A1129" s="4" t="inlineStr">
-        <is>
-          <t>Продукт</t>
-        </is>
-      </c>
-      <c r="B1129" s="5" t="inlineStr">
-        <is>
-          <t>Регистрация на тест-драйв</t>
-        </is>
-      </c>
-    </row>
-    <row r="1130" ht="24" customHeight="1">
-      <c r="A1130" s="4" t="inlineStr">
-        <is>
-          <t>Компонент</t>
-        </is>
-      </c>
-      <c r="B1130" s="5" t="inlineStr">
-        <is>
-          <t>Экран благодарности</t>
-        </is>
-      </c>
-    </row>
-    <row r="1131" ht="24" customHeight="1">
-      <c r="A1131" s="4" t="inlineStr">
-        <is>
-          <t>Серьёзность</t>
-        </is>
-      </c>
-      <c r="B1131" s="22" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="1132" ht="24" customHeight="1">
-      <c r="A1132" s="4" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="B1132" s="5" t="inlineStr"/>
-    </row>
-    <row r="1133" ht="24" customHeight="1">
-      <c r="A1133" s="4" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="B1133" s="5" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-    </row>
-    <row r="1134" ht="24" customHeight="1">
-      <c r="A1134" s="4" t="inlineStr">
-        <is>
-          <t>Автор</t>
-        </is>
-      </c>
-      <c r="B1134" s="5" t="inlineStr">
-        <is>
-          <t>Павел</t>
-        </is>
-      </c>
-    </row>
-    <row r="1135" ht="24" customHeight="1">
-      <c r="A1135" s="4" t="inlineStr">
-        <is>
-          <t>Дата обнаружения</t>
-        </is>
-      </c>
-      <c r="B1135" s="5" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="1136" ht="56" customHeight="1">
-      <c r="A1136" s="4" t="inlineStr">
-        <is>
-          <t>Окружение</t>
-        </is>
-      </c>
-      <c r="B1136" s="5" t="inlineStr">
-        <is>
-          <t>ОС: Linux, десктоп. Браузер: Google Chrome 148.0.7778.96. Окно: 1440×900, масштаб 100%. URL: https://testdrive.andersenlab.com/. Сборка страницы: Last-Modified 23.04.2026 13:11:09 GMT. Проверялась только десктопная версия.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1137" ht="24" customHeight="1">
-      <c r="A1137" s="4" t="inlineStr">
-        <is>
-          <t>Предусловия</t>
-        </is>
-      </c>
-      <c r="B1137" s="5" t="inlineStr">
-        <is>
-          <t>Открыто подтверждение с заполненными моделью и телефоном.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1138" ht="24" customHeight="1">
-      <c r="A1138" s="4" t="inlineStr">
-        <is>
-          <t>Тестовые данные</t>
-        </is>
-      </c>
-      <c r="B1138" s="5" t="inlineStr">
-        <is>
-          <t>Любая модель и телефон, которые уже видны на подтверждении.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1139" ht="56" customHeight="1">
-      <c r="A1139" s="4" t="inlineStr">
-        <is>
-          <t>Шаги воспроизведения</t>
-        </is>
-      </c>
-      <c r="B1139" s="5" t="inlineStr">
-        <is>
-          <t>1. Нажать Book.
-2. Прочитать экран благодарности.
-3. Найти на нём модель, конфигурацию, телефон и действие для новой заявки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1140" ht="56" customHeight="1">
-      <c r="A1140" s="4" t="inlineStr">
-        <is>
-          <t>Ожидаемый результат</t>
-        </is>
-      </c>
-      <c r="B1140" s="5" t="inlineStr">
-        <is>
-          <t>На экране повторяются модель, конфигурация и телефон с предыдущего шага. Есть понятное действие, чтобы начать другую заявку. Номер сохранённой заявки не ожидается: сохранение пользователя в этот модуль не входит.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1141" ht="56" customHeight="1">
-      <c r="A1141" s="4" t="inlineStr">
-        <is>
-          <t>Фактический результат</t>
-        </is>
-      </c>
-      <c r="B1141" s="5" t="inlineStr">
-        <is>
-          <t>На экране только «Thank you for booking the test drive!» и «Our managers will contact you within next 12 hours.» Модель и телефон не повторяются. Кнопки для новой заявки нет. Чтобы начать сначала, страницу нужно обновить вручную.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1142" ht="24" customHeight="1">
-      <c r="A1142" s="4" t="inlineStr">
-        <is>
-          <t>Воспроизводимость</t>
-        </is>
-      </c>
-      <c r="B1142" s="5" t="inlineStr">
-        <is>
-          <t>Всегда (5/5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="1143" ht="24" customHeight="1">
-      <c r="A1143" s="4" t="inlineStr">
-        <is>
-          <t>Вложение</t>
-        </is>
-      </c>
-      <c r="B1143" s="5" t="inlineStr">
-        <is>
-          <t>thank-you.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="1144" ht="24" customHeight="1">
-      <c r="A1144" s="4" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
-        </is>
-      </c>
-      <c r="B1144" s="5" t="inlineStr">
-        <is>
-          <t>Пропущенный артикль в фразе про 12 часов описан в BUG-015.</t>
-        </is>
-      </c>
-    </row>
-    <row r="1145" ht="18" customHeight="1">
-      <c r="A1145" s="23" t="inlineStr">
-        <is>
-          <t>Снимок</t>
-        </is>
-      </c>
-      <c r="B1145" s="24" t="inlineStr">
-        <is>
-          <t>thank-you.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="1146" ht="15" customHeight="1"/>
-    <row r="1147" ht="15" customHeight="1"/>
-    <row r="1148" ht="15" customHeight="1"/>
-    <row r="1149" ht="15" customHeight="1"/>
-    <row r="1150" ht="15" customHeight="1"/>
-    <row r="1151" ht="15" customHeight="1"/>
-    <row r="1152" ht="15" customHeight="1"/>
-    <row r="1153" ht="15" customHeight="1"/>
-    <row r="1154" ht="15" customHeight="1"/>
-    <row r="1155" ht="15" customHeight="1"/>
-    <row r="1156" ht="15" customHeight="1"/>
-    <row r="1157" ht="15" customHeight="1"/>
-    <row r="1158" ht="15" customHeight="1"/>
-    <row r="1159" ht="15" customHeight="1"/>
-    <row r="1160" ht="15" customHeight="1"/>
-    <row r="1161" ht="15" customHeight="1"/>
-    <row r="1162" ht="15" customHeight="1"/>
-    <row r="1163" ht="15" customHeight="1"/>
-    <row r="1164" ht="15" customHeight="1"/>
-    <row r="1165" ht="15" customHeight="1"/>
-    <row r="1166" ht="15" customHeight="1"/>
-    <row r="1167" ht="15" customHeight="1"/>
-    <row r="1168" ht="15" customHeight="1"/>
-    <row r="1169" ht="15" customHeight="1"/>
-    <row r="1170" ht="15" customHeight="1"/>
-    <row r="1171" ht="15" customHeight="1"/>
-    <row r="1172" ht="15" customHeight="1"/>
-    <row r="1173" ht="15" customHeight="1"/>
-    <row r="1174" ht="15" customHeight="1"/>
-    <row r="1175" ht="15" customHeight="1"/>
-    <row r="1176" ht="15" customHeight="1"/>
-    <row r="1177" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="19">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A530:B530"/>
     <mergeCell ref="A300:B300"/>
@@ -7894,7 +7467,6 @@
     <mergeCell ref="A998:B998"/>
     <mergeCell ref="A856:B856"/>
     <mergeCell ref="A706:B706"/>
-    <mergeCell ref="A1126:B1126"/>
     <mergeCell ref="A354:B354"/>
     <mergeCell ref="A652:B652"/>
     <mergeCell ref="A246:B246"/>
@@ -7907,7 +7479,7 @@
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="19" manualBreakCount="19">
+  <rowBreaks count="18" manualBreakCount="18">
     <brk id="29" min="0" max="16383" man="1"/>
     <brk id="83" min="0" max="16383" man="1"/>
     <brk id="137" min="0" max="16383" man="1"/>
@@ -7926,7 +7498,6 @@
     <brk id="997" min="0" max="16383" man="1"/>
     <brk id="1051" min="0" max="16383" man="1"/>
     <brk id="1071" min="0" max="16383" man="1"/>
-    <brk id="1125" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -7953,16 +7524,16 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Ниже наблюдения о функциях, которых в мастере нет. В баг-репорт они не поставлены: дефект — это расхождение уже реализованного поведения с ожидаемым, а не запрос новой функции.</t>
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Ниже наблюдения о функциях, которых в приложении нет. В баг-репорт они не поставлены: дефект — это расхождение уже реализованного поведения с ожидаемым, а не запрос новой функции.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>IMP-001   В мастере нет даты, времени и дилерского центра</t>
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>IMP-001   В приложении нет даты, времени и дилерского центра</t>
         </is>
       </c>
     </row>
@@ -8003,7 +7574,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>IMP-002   Перед Book нет согласия на обработку имени, возраста и телефона</t>
         </is>
@@ -8054,161 +7625,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Проверка</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Результат</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Вывод</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Фотографии трёх моделей</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>S500 Cabriolet AMG — кабриолет, GLC 250D 4MATIC — кроссовер, CLA SB Standard — универсал. Тип кузова на фото совпадает с подписью.</t>
-        </is>
-      </c>
-      <c r="C2" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Карусель при нажатии с паузой</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Стрелка вперёд идёт по кругу: S500 Cabriolet AMG, Cayenne 400, GLC 250D 4MATIC, CLA SB Standard. Стрелка назад с первой модели открывает последнюю.</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Списки двигателей S500 и CLA</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>S500 Cabriolet AMG: Petrol 3.0 и Petrol 3.5, коробка только Automatic. CLA SB Standard: Petrol 2.0 и Diesel 2.0, Automatic и Manual.</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Кириллица</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Фамилия Иванов, имя Иван, отчество Иванович отображаются в сводке без искажений.</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Разметка в имени</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Значение &lt;script&gt;alert(1)&lt;/script&gt; в имени выводится текстом. Диалоговое окно не появлялось.</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Путь с обычными данными</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Ivanov / Ivan / Ivanovich / 30 / +375291234567 для S500 Cabriolet AMG доходит до экрана благодарности. Ошибки текстов на этом пути описаны в BUG-014 и BUG-015.</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Консоль и ширина</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>При загрузке в консоли сообщений не было. На 1440×900 и 1280×800 при обычной длине имени горизонтальная прокрутка не появляется.</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>Дефекта нет</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/bug-reports/Баг-репорт_тест-драйв.xlsx
+++ b/bug-reports/Баг-репорт_тест-драйв.xlsx
@@ -1253,15 +1253,15 @@
       </c>
       <c r="D6" s="6" t="n"/>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Автор</t>
+          <t>Описание проекта</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Ваша задача - найти баги в системе. Так как нет документации, вы должны опираться на здравый смысл, общепринятую практику и пользовательский опыт. Всё, что противоречит этим трём критериям, подлежит заведению как баг.</t>
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
@@ -1269,12 +1269,12 @@
     <row r="8" ht="36" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Окружение</t>
+          <t>Автор</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ОС: Linux, десктоп. Браузер: Google Chrome 148.0.7778.96. Окно: 1440×900, масштаб 100%. URL: https://testdrive.andersenlab.com/. Сборка страницы: Last-Modified 23.04.2026 13:11:09 GMT. Проверялась только десктопная версия.</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
@@ -1282,25 +1282,25 @@
     <row r="9" ht="36" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Окружение</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ОС: Linux, десктоп. Браузер: Google Chrome 148.0.7778.96. Окно: 1440×900, масштаб 100%. URL: https://testdrive.andersenlab.com/. Сборка страницы: Last-Modified 23.04.2026 13:11:09 GMT. Проверялась только десктопная версия.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>Вне проверки</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Мобильная вёрстка, другие браузеры, сохранение пользователя и отправка писем. Последние два пункта исключены условием проверки.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Как устроен отчёт</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Один дефект — один отчёт. Заголовок начинается с экрана и называет наблюдаемую ошибку. Шаг содержит одно действие. Ожидаемый результат описывает поведение для пользователя и не предписывает способ исправления.</t>
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
@@ -1308,15 +1308,28 @@
     <row r="11" ht="48" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Как устроен отчёт</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Один дефект — один отчёт. Заголовок начинается с экрана и называет наблюдаемую ошибку. Шаг содержит одно действие. Ожидаемый результат описывает поведение для пользователя и не предписывает способ исправления.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Где читать</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Реестр — список для фильтра. Баг-репорты — полная карточка каждого дефекта и снимок. Улучшения — наблюдения, которые не оформлены как дефект.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
@@ -1419,7 +1432,8 @@
     </row>
     <row r="23" ht="22" customHeight="1"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
@@ -2189,7 +2203,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>BUG-020</t>
+          <t>BUG-019</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
@@ -7192,7 +7206,7 @@
     <row r="1072" ht="28" customHeight="1">
       <c r="A1072" s="17" t="inlineStr">
         <is>
-          <t>BUG-020   [Благодарность] После Book не показано, что именно забронировано</t>
+          <t>BUG-019   [Благодарность] После Book не показано, что именно забронировано</t>
         </is>
       </c>
       <c r="B1072" s="18" t="n"/>
@@ -7205,7 +7219,7 @@
       </c>
       <c r="B1073" s="5" t="inlineStr">
         <is>
-          <t>BUG-020</t>
+          <t>BUG-019</t>
         </is>
       </c>
     </row>
